--- a/1-7반.xlsx
+++ b/1-7반.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA0F142-C9CF-480E-9FE6-F67CF3A13A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{385F9E4D-213F-4B78-B73E-F78273391408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{94A5CD0E-065E-4B35-B399-E04F27AE39B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,418 +25,150 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="48">
   <si>
     <t>교시</t>
   </si>
   <si>
-    <t>월(24)</t>
-  </si>
-  <si>
-    <t>화(25)</t>
-  </si>
-  <si>
-    <t>수(26)</t>
-  </si>
-  <si>
-    <t>목(27)</t>
-  </si>
-  <si>
-    <t>금(28)</t>
+    <t>월(31)</t>
+  </si>
+  <si>
+    <t>화(1)</t>
+  </si>
+  <si>
+    <t>수(2)</t>
+  </si>
+  <si>
+    <t>목(3)</t>
+  </si>
+  <si>
+    <t>금(4)</t>
   </si>
   <si>
     <t>1(08:20)</t>
   </si>
   <si>
+    <t>체육A</t>
+  </si>
+  <si>
+    <t>윤승</t>
+  </si>
+  <si>
+    <t>공영B</t>
+  </si>
+  <si>
+    <t>유승</t>
+  </si>
+  <si>
+    <t>통사2</t>
+  </si>
+  <si>
+    <t>김형</t>
+  </si>
+  <si>
+    <t>공국B</t>
+  </si>
+  <si>
+    <t>김남</t>
+  </si>
+  <si>
+    <t>통과C</t>
+  </si>
+  <si>
+    <t>이자</t>
+  </si>
+  <si>
     <t>2(09:20)</t>
   </si>
   <si>
+    <t>공영A</t>
+  </si>
+  <si>
+    <t>김소</t>
+  </si>
+  <si>
+    <t>공수2</t>
+  </si>
+  <si>
+    <t>김수</t>
+  </si>
+  <si>
+    <t>체육B</t>
+  </si>
+  <si>
+    <t>김태</t>
+  </si>
+  <si>
     <t>3(10:20)</t>
   </si>
   <si>
+    <t>공국A</t>
+  </si>
+  <si>
+    <t>장환</t>
+  </si>
+  <si>
+    <t>한국2</t>
+  </si>
+  <si>
+    <t>김효</t>
+  </si>
+  <si>
+    <t>한자</t>
+  </si>
+  <si>
+    <t>주석</t>
+  </si>
+  <si>
     <t>4(11:20)</t>
   </si>
   <si>
+    <t>통과D</t>
+  </si>
+  <si>
+    <t>박소</t>
+  </si>
+  <si>
+    <t>통과A</t>
+  </si>
+  <si>
+    <t>안재</t>
+  </si>
+  <si>
     <t>5(13:00)</t>
   </si>
   <si>
+    <t>과실2</t>
+  </si>
+  <si>
     <t>6(14:00)</t>
   </si>
   <si>
+    <t>미술</t>
+  </si>
+  <si>
+    <t>권혜</t>
+  </si>
+  <si>
+    <t>통과B</t>
+  </si>
+  <si>
+    <t>이정</t>
+  </si>
+  <si>
+    <t>창진</t>
+  </si>
+  <si>
+    <t>최상</t>
+  </si>
+  <si>
     <t>7(15:00)</t>
   </si>
   <si>
-    <t>창진</t>
-  </si>
-  <si>
-    <t>체육A</t>
-  </si>
-  <si>
-    <t>공영B</t>
-  </si>
-  <si>
-    <t>공수2</t>
-  </si>
-  <si>
-    <t>공국B</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>윤승</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>희</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>유승희</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>김수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>진</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>김남</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>훈</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>공영A</t>
-  </si>
-  <si>
-    <t>통사2</t>
-  </si>
-  <si>
-    <t>통과C</t>
-  </si>
-  <si>
-    <t>한국2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>김소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>혜</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>김형</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>중</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>영</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>김효</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>인</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>공국A</t>
-  </si>
-  <si>
-    <t>한자</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>장환</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>준</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>주석</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>준</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>장환준</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>체육B</t>
-  </si>
-  <si>
-    <t>통과D</t>
-  </si>
-  <si>
-    <t>통과A</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>김태</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>헌</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>박소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>희</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>안재익</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>주석준</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>과실2</t>
+    <t>8(16:00)</t>
   </si>
   <si>
     <t>동아리</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>미술</t>
-  </si>
-  <si>
-    <t>통과B</t>
-  </si>
-  <si>
-    <t>권혜민</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>훈</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>최상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>백</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -444,7 +176,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,13 +197,6 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="9"/>
@@ -556,7 +281,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -566,22 +291,25 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -897,8 +625,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A47EFDA-F254-44E7-ACE8-EF70EAAB00AF}">
-  <dimension ref="A1:F15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE5BED3-01AE-4902-AED2-33B95BFF7481}">
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -926,262 +654,271 @@
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
-      <c r="B3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>20</v>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
-      <c r="B5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>29</v>
+      <c r="B5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
-      <c r="B7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>34</v>
+      <c r="B7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6"/>
-      <c r="B9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>41</v>
+      <c r="B9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>43</v>
+        <v>20</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
-      <c r="B11" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="7" t="s">
+      <c r="B11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="4"/>
+      <c r="C11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="8" t="s">
         <v>43</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6"/>
-      <c r="B13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="4"/>
+      <c r="B13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6"/>
-      <c r="B15" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="7" t="s">
+      <c r="B15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="F10:F11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="A14:A15"/>
@@ -1191,9 +928,10 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="F10:F11"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" copies="0" r:id="rId1"/>
 </worksheet>
 </file>